--- a/data/raw/01_FormatosRA_ReformaCurricular/FormatoRA_MCE_PBOG.xlsx
+++ b/data/raw/01_FormatosRA_ReformaCurricular/FormatoRA_MCE_PBOG.xlsx
@@ -3772,13 +3772,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3791,24 +3791,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3817,14 +3799,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3850,13 +3832,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3895,6 +3895,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3904,13 +3910,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8659,16 +8659,16 @@
       <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="110" t="s">
+      <c r="E1" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110" t="s">
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
       <c r="K1" s="42" t="s">
         <v>6</v>
       </c>
@@ -8709,10 +8709,10 @@
       </c>
     </row>
     <row r="3" spans="1:11" s="6" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="112" t="s">
+      <c r="A3" s="110" t="s">
         <v>578</v>
       </c>
-      <c r="B3" s="112" t="s">
+      <c r="B3" s="110" t="s">
         <v>579</v>
       </c>
       <c r="C3" s="111" t="s">
@@ -8744,8 +8744,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" s="6" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="94"/>
       <c r="C4" s="88"/>
       <c r="D4" s="88"/>
       <c r="E4" s="6" t="s">
@@ -8763,8 +8763,8 @@
       <c r="K4" s="88"/>
     </row>
     <row r="5" spans="1:11" s="6" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="85"/>
-      <c r="B5" s="85"/>
+      <c r="A5" s="94"/>
+      <c r="B5" s="94"/>
       <c r="C5" s="88"/>
       <c r="D5" s="88"/>
       <c r="E5" s="6" t="s">
@@ -8898,16 +8898,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="C3:C5"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="H3:H5"/>
     <mergeCell ref="I3:I5"/>
     <mergeCell ref="J3:J5"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="C3:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9545,8 +9545,8 @@
       <c r="A4" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="100"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="105"/>
       <c r="D4" s="26" t="s">
         <v>604</v>
       </c>
@@ -9559,8 +9559,8 @@
       <c r="A5" s="30" t="s">
         <v>598</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="101"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="106"/>
       <c r="D5" s="57" t="s">
         <v>605</v>
       </c>
@@ -9573,10 +9573,10 @@
       <c r="A6" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="85" t="s">
         <v>608</v>
       </c>
-      <c r="C6" s="100" t="s">
+      <c r="C6" s="105" t="s">
         <v>609</v>
       </c>
       <c r="D6" s="26" t="s">
@@ -9593,8 +9593,8 @@
       <c r="A7" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="B7" s="91"/>
-      <c r="C7" s="100"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="26" t="s">
         <v>611</v>
       </c>
@@ -9607,8 +9607,8 @@
       <c r="A8" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="B8" s="91"/>
-      <c r="C8" s="100"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="105"/>
       <c r="D8" s="26" t="s">
         <v>605</v>
       </c>
@@ -9621,8 +9621,8 @@
       <c r="A9" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="B9" s="91"/>
-      <c r="C9" s="100"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="105"/>
       <c r="D9" s="26"/>
       <c r="E9" s="114"/>
       <c r="F9" s="5"/>
@@ -9631,8 +9631,8 @@
       <c r="A10" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B10" s="91"/>
-      <c r="C10" s="100"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="105"/>
       <c r="D10" s="26"/>
       <c r="E10" s="114"/>
     </row>
@@ -9640,8 +9640,8 @@
       <c r="A11" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="B11" s="91"/>
-      <c r="C11" s="100"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="105"/>
       <c r="D11" s="26"/>
       <c r="E11" s="114"/>
     </row>
@@ -9679,8 +9679,8 @@
       <c r="A14" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="B14" s="91"/>
-      <c r="C14" s="100"/>
+      <c r="B14" s="85"/>
+      <c r="C14" s="105"/>
       <c r="D14" s="26" t="s">
         <v>605</v>
       </c>
@@ -9693,8 +9693,8 @@
       <c r="A15" s="30" t="s">
         <v>600</v>
       </c>
-      <c r="B15" s="92"/>
-      <c r="C15" s="101"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="106"/>
       <c r="D15" s="57"/>
       <c r="E15" s="115"/>
       <c r="F15" s="30"/>
@@ -9765,10 +9765,10 @@
       <c r="F1" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="105" t="s">
+      <c r="G1" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="106"/>
+      <c r="H1" s="100"/>
       <c r="I1" s="41" t="s">
         <v>70</v>
       </c>
@@ -9852,47 +9852,47 @@
       <c r="B3" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="C3" s="85">
+      <c r="C3" s="94">
         <v>1</v>
       </c>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="94" t="s">
         <v>652</v>
       </c>
       <c r="E3" s="88" t="s">
         <v>643</v>
       </c>
-      <c r="F3" s="91" t="s">
+      <c r="F3" s="85" t="s">
         <v>615</v>
       </c>
-      <c r="G3" s="91" t="s">
+      <c r="G3" s="85" t="s">
         <v>616</v>
       </c>
-      <c r="H3" s="91"/>
-      <c r="I3" s="91">
+      <c r="H3" s="85"/>
+      <c r="I3" s="85">
         <v>3</v>
       </c>
-      <c r="J3" s="91">
+      <c r="J3" s="85">
         <f>12*I3</f>
         <v>36</v>
       </c>
-      <c r="K3" s="91">
+      <c r="K3" s="85">
         <f>36*I3</f>
         <v>108</v>
       </c>
-      <c r="L3" s="91">
+      <c r="L3" s="85">
         <f>SUM(J3:K5)</f>
         <v>144</v>
       </c>
-      <c r="M3" s="103" t="s">
+      <c r="M3" s="97" t="s">
         <v>621</v>
       </c>
-      <c r="N3" s="103" t="s">
+      <c r="N3" s="97" t="s">
         <v>647</v>
       </c>
-      <c r="O3" s="97" t="s">
+      <c r="O3" s="91" t="s">
         <v>617</v>
       </c>
-      <c r="P3" s="103" t="s">
+      <c r="P3" s="97" t="s">
         <v>92</v>
       </c>
       <c r="Q3" s="5" t="s">
@@ -9907,20 +9907,20 @@
       <c r="B4" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="88"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="103"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="97"/>
-      <c r="P4" s="103"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="97"/>
     </row>
     <row r="5" spans="1:17" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="30" t="str">
@@ -9930,20 +9930,20 @@
       <c r="B5" s="30" t="s">
         <v>594</v>
       </c>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
       <c r="E5" s="89"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="92"/>
-      <c r="K5" s="92"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="98"/>
-      <c r="P5" s="104"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="86"/>
+      <c r="K5" s="86"/>
+      <c r="L5" s="86"/>
+      <c r="M5" s="98"/>
+      <c r="N5" s="98"/>
+      <c r="O5" s="92"/>
+      <c r="P5" s="98"/>
     </row>
     <row r="6" spans="1:17" ht="36" x14ac:dyDescent="0.5">
       <c r="A6" s="31" t="str">
@@ -9953,47 +9953,47 @@
       <c r="B6" s="32" t="s">
         <v>592</v>
       </c>
-      <c r="C6" s="84">
+      <c r="C6" s="93">
         <v>1</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="93" t="s">
         <v>651</v>
       </c>
-      <c r="E6" s="107" t="s">
+      <c r="E6" s="101" t="s">
         <v>662</v>
       </c>
-      <c r="F6" s="84" t="s">
+      <c r="F6" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G6" s="90" t="s">
+      <c r="G6" s="84" t="s">
         <v>616</v>
       </c>
-      <c r="H6" s="90"/>
-      <c r="I6" s="90">
+      <c r="H6" s="84"/>
+      <c r="I6" s="84">
         <v>3</v>
       </c>
-      <c r="J6" s="90">
+      <c r="J6" s="84">
         <f>12*I6</f>
         <v>36</v>
       </c>
-      <c r="K6" s="90">
+      <c r="K6" s="84">
         <f>36*I6</f>
         <v>108</v>
       </c>
-      <c r="L6" s="90">
+      <c r="L6" s="84">
         <f>SUM(J6:K8)</f>
         <v>144</v>
       </c>
-      <c r="M6" s="102" t="s">
+      <c r="M6" s="96" t="s">
         <v>618</v>
       </c>
-      <c r="N6" s="102" t="s">
+      <c r="N6" s="96" t="s">
         <v>646</v>
       </c>
-      <c r="O6" s="96" t="s">
+      <c r="O6" s="90" t="s">
         <v>617</v>
       </c>
-      <c r="P6" s="102" t="s">
+      <c r="P6" s="96" t="s">
         <v>94</v>
       </c>
     </row>
@@ -10005,20 +10005,20 @@
       <c r="B7" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="103"/>
-      <c r="O7" s="97"/>
-      <c r="P7" s="103"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
+      <c r="I7" s="85"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="91"/>
+      <c r="P7" s="97"/>
     </row>
     <row r="8" spans="1:17" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="30" t="str">
@@ -10028,20 +10028,20 @@
       <c r="B8" s="34" t="s">
         <v>598</v>
       </c>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="109"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="92"/>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="104"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="104"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="95"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="92"/>
+      <c r="P8" s="98"/>
     </row>
     <row r="9" spans="1:17" ht="36" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="str">
@@ -10051,47 +10051,47 @@
       <c r="B9" s="31" t="s">
         <v>592</v>
       </c>
-      <c r="C9" s="84">
+      <c r="C9" s="93">
         <v>1</v>
       </c>
-      <c r="D9" s="84" t="s">
+      <c r="D9" s="93" t="s">
         <v>650</v>
       </c>
       <c r="E9" s="87" t="s">
         <v>663</v>
       </c>
-      <c r="F9" s="84" t="s">
+      <c r="F9" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G9" s="90" t="s">
+      <c r="G9" s="84" t="s">
         <v>616</v>
       </c>
-      <c r="H9" s="90"/>
-      <c r="I9" s="90">
+      <c r="H9" s="84"/>
+      <c r="I9" s="84">
         <v>3</v>
       </c>
-      <c r="J9" s="90">
+      <c r="J9" s="84">
         <f>12*I9</f>
         <v>36</v>
       </c>
-      <c r="K9" s="90">
+      <c r="K9" s="84">
         <f>36*I9</f>
         <v>108</v>
       </c>
-      <c r="L9" s="90">
+      <c r="L9" s="84">
         <f>SUM(J9:K9)</f>
         <v>144</v>
       </c>
-      <c r="M9" s="96" t="s">
+      <c r="M9" s="90" t="s">
         <v>620</v>
       </c>
-      <c r="N9" s="102" t="s">
+      <c r="N9" s="96" t="s">
         <v>646</v>
       </c>
-      <c r="O9" s="96" t="s">
+      <c r="O9" s="90" t="s">
         <v>617</v>
       </c>
-      <c r="P9" s="102" t="s">
+      <c r="P9" s="96" t="s">
         <v>92</v>
       </c>
     </row>
@@ -10103,20 +10103,20 @@
       <c r="B10" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
       <c r="E10" s="88"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="91"/>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="91"/>
-      <c r="M10" s="97"/>
-      <c r="N10" s="103"/>
-      <c r="O10" s="97"/>
-      <c r="P10" s="103"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="97"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="97"/>
     </row>
     <row r="11" spans="1:17" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="str">
@@ -10126,20 +10126,20 @@
       <c r="B11" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
       <c r="E11" s="88"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="91"/>
-      <c r="K11" s="91"/>
-      <c r="L11" s="91"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="103"/>
-      <c r="O11" s="97"/>
-      <c r="P11" s="103"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="91"/>
+      <c r="N11" s="97"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="97"/>
     </row>
     <row r="12" spans="1:17" ht="108" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="str">
@@ -10149,20 +10149,20 @@
       <c r="B12" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
       <c r="E12" s="88"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="91"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="97"/>
-      <c r="N12" s="103"/>
-      <c r="O12" s="97"/>
-      <c r="P12" s="103"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="97"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="97"/>
     </row>
     <row r="13" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="str">
@@ -10172,20 +10172,20 @@
       <c r="B13" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
       <c r="E13" s="88"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="97"/>
-      <c r="N13" s="103"/>
-      <c r="O13" s="97"/>
-      <c r="P13" s="103"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="91"/>
+      <c r="N13" s="97"/>
+      <c r="O13" s="91"/>
+      <c r="P13" s="97"/>
     </row>
     <row r="14" spans="1:17" ht="54" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="str">
@@ -10195,20 +10195,20 @@
       <c r="B14" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="C14" s="85"/>
-      <c r="D14" s="85"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
       <c r="E14" s="88"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="91"/>
-      <c r="M14" s="97"/>
-      <c r="N14" s="103"/>
-      <c r="O14" s="97"/>
-      <c r="P14" s="103"/>
+      <c r="F14" s="94"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="97"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="97"/>
     </row>
     <row r="15" spans="1:17" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="30" t="str">
@@ -10218,20 +10218,20 @@
       <c r="B15" s="30" t="s">
         <v>600</v>
       </c>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
       <c r="E15" s="89"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="92"/>
-      <c r="M15" s="98"/>
-      <c r="N15" s="104"/>
-      <c r="O15" s="98"/>
-      <c r="P15" s="104"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="98"/>
+      <c r="O15" s="92"/>
+      <c r="P15" s="98"/>
     </row>
     <row r="16" spans="1:17" ht="36" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="str">
@@ -10241,34 +10241,34 @@
       <c r="B16" s="31" t="s">
         <v>592</v>
       </c>
-      <c r="C16" s="84">
+      <c r="C16" s="93">
         <v>1</v>
       </c>
-      <c r="D16" s="84" t="s">
+      <c r="D16" s="93" t="s">
         <v>614</v>
       </c>
       <c r="E16" s="87" t="s">
         <v>644</v>
       </c>
-      <c r="F16" s="84" t="s">
+      <c r="F16" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G16" s="84" t="s">
+      <c r="G16" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="H16" s="84"/>
-      <c r="I16" s="90">
+      <c r="H16" s="93"/>
+      <c r="I16" s="84">
         <v>3</v>
       </c>
-      <c r="J16" s="90">
+      <c r="J16" s="84">
         <f>I16*12</f>
         <v>36</v>
       </c>
-      <c r="K16" s="90">
+      <c r="K16" s="84">
         <f>I16*32</f>
         <v>96</v>
       </c>
-      <c r="L16" s="90">
+      <c r="L16" s="84">
         <f>SUM(J16:K16)</f>
         <v>132</v>
       </c>
@@ -10278,10 +10278,10 @@
       <c r="N16" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O16" s="96" t="s">
+      <c r="O16" s="90" t="s">
         <v>617</v>
       </c>
-      <c r="P16" s="102" t="s">
+      <c r="P16" s="96" t="s">
         <v>92</v>
       </c>
     </row>
@@ -10293,20 +10293,20 @@
       <c r="B17" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
       <c r="E17" s="88"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="85"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="85"/>
       <c r="M17" s="88"/>
       <c r="N17" s="88"/>
-      <c r="O17" s="97"/>
-      <c r="P17" s="103"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="97"/>
     </row>
     <row r="18" spans="1:16" ht="108" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="str">
@@ -10316,20 +10316,20 @@
       <c r="B18" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
       <c r="E18" s="88"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="91"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="91"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="85"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="85"/>
       <c r="M18" s="88"/>
       <c r="N18" s="88"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="103"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="97"/>
     </row>
     <row r="19" spans="1:16" ht="90" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="str">
@@ -10339,20 +10339,20 @@
       <c r="B19" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
       <c r="E19" s="88"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="91"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="91"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="85"/>
+      <c r="K19" s="85"/>
+      <c r="L19" s="85"/>
       <c r="M19" s="88"/>
       <c r="N19" s="88"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="103"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="97"/>
     </row>
     <row r="20" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="30" t="str">
@@ -10362,20 +10362,20 @@
       <c r="B20" s="30" t="s">
         <v>600</v>
       </c>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
+      <c r="C20" s="95"/>
+      <c r="D20" s="95"/>
       <c r="E20" s="89"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="92"/>
-      <c r="J20" s="92"/>
-      <c r="K20" s="92"/>
-      <c r="L20" s="92"/>
+      <c r="F20" s="95"/>
+      <c r="G20" s="95"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
       <c r="M20" s="89"/>
       <c r="N20" s="89"/>
-      <c r="O20" s="98"/>
-      <c r="P20" s="104"/>
+      <c r="O20" s="92"/>
+      <c r="P20" s="98"/>
     </row>
     <row r="21" spans="1:16" ht="36" x14ac:dyDescent="0.3">
       <c r="A21" s="31" t="str">
@@ -10385,44 +10385,44 @@
       <c r="B21" s="33" t="s">
         <v>592</v>
       </c>
-      <c r="C21" s="84">
+      <c r="C21" s="93">
         <v>1</v>
       </c>
-      <c r="D21" s="84" t="s">
+      <c r="D21" s="93" t="s">
         <v>653</v>
       </c>
       <c r="E21" s="87" t="s">
         <v>665</v>
       </c>
-      <c r="F21" s="84" t="s">
+      <c r="F21" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G21" s="84" t="s">
+      <c r="G21" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="H21" s="90"/>
-      <c r="I21" s="93">
+      <c r="H21" s="84"/>
+      <c r="I21" s="107">
         <v>3</v>
       </c>
-      <c r="J21" s="90">
+      <c r="J21" s="84">
         <f>12*I21</f>
         <v>36</v>
       </c>
-      <c r="K21" s="90">
+      <c r="K21" s="84">
         <f>36*I21</f>
         <v>108</v>
       </c>
-      <c r="L21" s="90">
+      <c r="L21" s="84">
         <f>SUM(J21:K24)</f>
         <v>144</v>
       </c>
-      <c r="M21" s="99" t="s">
+      <c r="M21" s="104" t="s">
         <v>622</v>
       </c>
       <c r="N21" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O21" s="96" t="s">
+      <c r="O21" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P21" s="87" t="s">
@@ -10437,19 +10437,19 @@
       <c r="B22" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="94"/>
       <c r="E22" s="88"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="91"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="91"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="91"/>
-      <c r="M22" s="100"/>
+      <c r="F22" s="94"/>
+      <c r="G22" s="94"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="108"/>
+      <c r="J22" s="85"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="105"/>
       <c r="N22" s="88"/>
-      <c r="O22" s="97"/>
+      <c r="O22" s="91"/>
       <c r="P22" s="88"/>
     </row>
     <row r="23" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -10460,19 +10460,19 @@
       <c r="B23" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
+      <c r="C23" s="94"/>
+      <c r="D23" s="94"/>
       <c r="E23" s="88"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="94"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="91"/>
-      <c r="M23" s="100"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="108"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="105"/>
       <c r="N23" s="88"/>
-      <c r="O23" s="97"/>
+      <c r="O23" s="91"/>
       <c r="P23" s="88"/>
     </row>
     <row r="24" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -10483,19 +10483,19 @@
       <c r="B24" s="30" t="s">
         <v>600</v>
       </c>
-      <c r="C24" s="86"/>
-      <c r="D24" s="86"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
       <c r="E24" s="89"/>
-      <c r="F24" s="86"/>
-      <c r="G24" s="86"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="95"/>
-      <c r="J24" s="92"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="101"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="109"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="106"/>
       <c r="N24" s="89"/>
-      <c r="O24" s="98"/>
+      <c r="O24" s="92"/>
       <c r="P24" s="89"/>
     </row>
     <row r="25" spans="1:16" ht="36" x14ac:dyDescent="0.3">
@@ -10506,34 +10506,34 @@
       <c r="B25" s="31" t="s">
         <v>592</v>
       </c>
-      <c r="C25" s="84">
+      <c r="C25" s="93">
         <v>2</v>
       </c>
-      <c r="D25" s="84" t="s">
+      <c r="D25" s="93" t="s">
         <v>623</v>
       </c>
       <c r="E25" s="87" t="s">
         <v>666</v>
       </c>
-      <c r="F25" s="84" t="s">
+      <c r="F25" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G25" s="84"/>
-      <c r="H25" s="84" t="s">
+      <c r="G25" s="93"/>
+      <c r="H25" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I25" s="84">
+      <c r="I25" s="93">
         <v>2</v>
       </c>
-      <c r="J25" s="84">
+      <c r="J25" s="93">
         <f>12*I25</f>
         <v>24</v>
       </c>
-      <c r="K25" s="84">
+      <c r="K25" s="93">
         <f>36*I25</f>
         <v>72</v>
       </c>
-      <c r="L25" s="84">
+      <c r="L25" s="93">
         <f>SUM(J25:K27)</f>
         <v>96</v>
       </c>
@@ -10543,7 +10543,7 @@
       <c r="N25" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O25" s="96" t="s">
+      <c r="O25" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P25" s="87" t="s">
@@ -10558,19 +10558,19 @@
       <c r="B26" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="C26" s="85"/>
-      <c r="D26" s="85"/>
+      <c r="C26" s="94"/>
+      <c r="D26" s="94"/>
       <c r="E26" s="88"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
+      <c r="F26" s="94"/>
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="94"/>
+      <c r="K26" s="94"/>
+      <c r="L26" s="94"/>
       <c r="M26" s="88"/>
       <c r="N26" s="88"/>
-      <c r="O26" s="97"/>
+      <c r="O26" s="91"/>
       <c r="P26" s="88"/>
     </row>
     <row r="27" spans="1:16" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -10581,19 +10581,19 @@
       <c r="B27" s="30" t="s">
         <v>595</v>
       </c>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="95"/>
       <c r="E27" s="89"/>
-      <c r="F27" s="86"/>
-      <c r="G27" s="86"/>
-      <c r="H27" s="86"/>
-      <c r="I27" s="86"/>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="86"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+      <c r="H27" s="95"/>
+      <c r="I27" s="95"/>
+      <c r="J27" s="95"/>
+      <c r="K27" s="95"/>
+      <c r="L27" s="95"/>
       <c r="M27" s="89"/>
       <c r="N27" s="89"/>
-      <c r="O27" s="98"/>
+      <c r="O27" s="92"/>
       <c r="P27" s="89"/>
     </row>
     <row r="28" spans="1:16" ht="36" x14ac:dyDescent="0.3">
@@ -10604,34 +10604,34 @@
       <c r="B28" s="31" t="s">
         <v>592</v>
       </c>
-      <c r="C28" s="84">
+      <c r="C28" s="93">
         <v>2</v>
       </c>
-      <c r="D28" s="84" t="s">
+      <c r="D28" s="93" t="s">
         <v>654</v>
       </c>
       <c r="E28" s="87" t="s">
         <v>645</v>
       </c>
-      <c r="F28" s="84" t="s">
+      <c r="F28" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G28" s="84"/>
-      <c r="H28" s="84" t="s">
+      <c r="G28" s="93"/>
+      <c r="H28" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I28" s="90">
+      <c r="I28" s="84">
         <v>2</v>
       </c>
-      <c r="J28" s="90">
+      <c r="J28" s="84">
         <f>I28*12</f>
         <v>24</v>
       </c>
-      <c r="K28" s="90">
+      <c r="K28" s="84">
         <f>I28*36</f>
         <v>72</v>
       </c>
-      <c r="L28" s="90">
+      <c r="L28" s="84">
         <f>SUM(J28:K33)</f>
         <v>96</v>
       </c>
@@ -10641,7 +10641,7 @@
       <c r="N28" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O28" s="96" t="s">
+      <c r="O28" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P28" s="87" t="s">
@@ -10656,19 +10656,19 @@
       <c r="B29" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="94"/>
       <c r="E29" s="88"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="91"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="91"/>
+      <c r="F29" s="94"/>
+      <c r="G29" s="94"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="85"/>
+      <c r="J29" s="85"/>
+      <c r="K29" s="85"/>
+      <c r="L29" s="85"/>
       <c r="M29" s="88"/>
       <c r="N29" s="88"/>
-      <c r="O29" s="97"/>
+      <c r="O29" s="91"/>
       <c r="P29" s="88"/>
     </row>
     <row r="30" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -10679,19 +10679,19 @@
       <c r="B30" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="C30" s="85"/>
-      <c r="D30" s="85"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
       <c r="E30" s="88"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="91"/>
-      <c r="K30" s="91"/>
-      <c r="L30" s="91"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="94"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="85"/>
+      <c r="K30" s="85"/>
+      <c r="L30" s="85"/>
       <c r="M30" s="88"/>
       <c r="N30" s="88"/>
-      <c r="O30" s="97"/>
+      <c r="O30" s="91"/>
       <c r="P30" s="88"/>
     </row>
     <row r="31" spans="1:16" ht="72" x14ac:dyDescent="0.3">
@@ -10702,19 +10702,19 @@
       <c r="B31" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="C31" s="85"/>
-      <c r="D31" s="85"/>
+      <c r="C31" s="94"/>
+      <c r="D31" s="94"/>
       <c r="E31" s="88"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="91"/>
-      <c r="K31" s="91"/>
-      <c r="L31" s="91"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="94"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="85"/>
+      <c r="J31" s="85"/>
+      <c r="K31" s="85"/>
+      <c r="L31" s="85"/>
       <c r="M31" s="88"/>
       <c r="N31" s="88"/>
-      <c r="O31" s="97"/>
+      <c r="O31" s="91"/>
       <c r="P31" s="88"/>
     </row>
     <row r="32" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -10725,19 +10725,19 @@
       <c r="B32" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="94"/>
       <c r="E32" s="88"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
-      <c r="L32" s="91"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="85"/>
+      <c r="K32" s="85"/>
+      <c r="L32" s="85"/>
       <c r="M32" s="88"/>
       <c r="N32" s="88"/>
-      <c r="O32" s="97"/>
+      <c r="O32" s="91"/>
       <c r="P32" s="88" t="s">
         <v>95</v>
       </c>
@@ -10750,19 +10750,19 @@
       <c r="B33" s="30" t="s">
         <v>600</v>
       </c>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="95"/>
       <c r="E33" s="89"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="86"/>
-      <c r="H33" s="86"/>
-      <c r="I33" s="92"/>
-      <c r="J33" s="92"/>
-      <c r="K33" s="92"/>
-      <c r="L33" s="92"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="95"/>
+      <c r="H33" s="95"/>
+      <c r="I33" s="86"/>
+      <c r="J33" s="86"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
       <c r="M33" s="89"/>
       <c r="N33" s="89"/>
-      <c r="O33" s="98"/>
+      <c r="O33" s="92"/>
       <c r="P33" s="89"/>
     </row>
     <row r="34" spans="1:16" ht="36" x14ac:dyDescent="0.3">
@@ -10773,34 +10773,34 @@
       <c r="B34" s="31" t="s">
         <v>592</v>
       </c>
-      <c r="C34" s="84">
+      <c r="C34" s="93">
         <v>2</v>
       </c>
-      <c r="D34" s="84" t="s">
+      <c r="D34" s="93" t="s">
         <v>624</v>
       </c>
       <c r="E34" s="87" t="s">
         <v>669</v>
       </c>
-      <c r="F34" s="84" t="s">
+      <c r="F34" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G34" s="84"/>
-      <c r="H34" s="84" t="s">
+      <c r="G34" s="93"/>
+      <c r="H34" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I34" s="90">
+      <c r="I34" s="84">
         <v>3</v>
       </c>
-      <c r="J34" s="90">
+      <c r="J34" s="84">
         <f>I34*12</f>
         <v>36</v>
       </c>
-      <c r="K34" s="90">
+      <c r="K34" s="84">
         <f>I34*36</f>
         <v>108</v>
       </c>
-      <c r="L34" s="90">
+      <c r="L34" s="84">
         <f>SUM(J34:K34)</f>
         <v>144</v>
       </c>
@@ -10810,7 +10810,7 @@
       <c r="N34" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O34" s="96" t="s">
+      <c r="O34" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P34" s="87" t="s">
@@ -10825,19 +10825,19 @@
       <c r="B35" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="C35" s="85"/>
-      <c r="D35" s="85"/>
+      <c r="C35" s="94"/>
+      <c r="D35" s="94"/>
       <c r="E35" s="88"/>
-      <c r="F35" s="85"/>
-      <c r="G35" s="85"/>
-      <c r="H35" s="85"/>
-      <c r="I35" s="91"/>
-      <c r="J35" s="91"/>
-      <c r="K35" s="91"/>
-      <c r="L35" s="91"/>
+      <c r="F35" s="94"/>
+      <c r="G35" s="94"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="85"/>
+      <c r="J35" s="85"/>
+      <c r="K35" s="85"/>
+      <c r="L35" s="85"/>
       <c r="M35" s="88"/>
       <c r="N35" s="88"/>
-      <c r="O35" s="97"/>
+      <c r="O35" s="91"/>
       <c r="P35" s="88"/>
     </row>
     <row r="36" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -10848,19 +10848,19 @@
       <c r="B36" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="C36" s="85"/>
-      <c r="D36" s="85"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="94"/>
       <c r="E36" s="88"/>
-      <c r="F36" s="85"/>
-      <c r="G36" s="85"/>
-      <c r="H36" s="85"/>
-      <c r="I36" s="91"/>
-      <c r="J36" s="91"/>
-      <c r="K36" s="91"/>
-      <c r="L36" s="91"/>
+      <c r="F36" s="94"/>
+      <c r="G36" s="94"/>
+      <c r="H36" s="94"/>
+      <c r="I36" s="85"/>
+      <c r="J36" s="85"/>
+      <c r="K36" s="85"/>
+      <c r="L36" s="85"/>
       <c r="M36" s="88"/>
       <c r="N36" s="88"/>
-      <c r="O36" s="97"/>
+      <c r="O36" s="91"/>
       <c r="P36" s="88"/>
     </row>
     <row r="37" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -10871,19 +10871,19 @@
       <c r="B37" s="30" t="s">
         <v>598</v>
       </c>
-      <c r="C37" s="86"/>
-      <c r="D37" s="86"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
       <c r="E37" s="89"/>
-      <c r="F37" s="86"/>
-      <c r="G37" s="86"/>
-      <c r="H37" s="86"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="92"/>
-      <c r="K37" s="92"/>
-      <c r="L37" s="92"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
+      <c r="I37" s="86"/>
+      <c r="J37" s="86"/>
+      <c r="K37" s="86"/>
+      <c r="L37" s="86"/>
       <c r="M37" s="89"/>
       <c r="N37" s="89"/>
-      <c r="O37" s="98"/>
+      <c r="O37" s="92"/>
       <c r="P37" s="89"/>
     </row>
     <row r="38" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -10894,34 +10894,34 @@
       <c r="B38" s="31" t="s">
         <v>594</v>
       </c>
-      <c r="C38" s="84">
+      <c r="C38" s="93">
         <v>2</v>
       </c>
-      <c r="D38" s="84" t="s">
+      <c r="D38" s="93" t="s">
         <v>625</v>
       </c>
       <c r="E38" s="87" t="s">
         <v>626</v>
       </c>
-      <c r="F38" s="84" t="s">
+      <c r="F38" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G38" s="84"/>
-      <c r="H38" s="84" t="s">
+      <c r="G38" s="93"/>
+      <c r="H38" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I38" s="90">
+      <c r="I38" s="84">
         <v>3</v>
       </c>
-      <c r="J38" s="90">
+      <c r="J38" s="84">
         <f>I38*12</f>
         <v>36</v>
       </c>
-      <c r="K38" s="90">
+      <c r="K38" s="84">
         <f>I38*36</f>
         <v>108</v>
       </c>
-      <c r="L38" s="90">
+      <c r="L38" s="84">
         <f>SUM(J38:K38)</f>
         <v>144</v>
       </c>
@@ -10931,7 +10931,7 @@
       <c r="N38" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O38" s="96" t="s">
+      <c r="O38" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P38" s="87" t="s">
@@ -10946,19 +10946,19 @@
       <c r="B39" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
       <c r="E39" s="88"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="91"/>
+      <c r="F39" s="94"/>
+      <c r="G39" s="94"/>
+      <c r="H39" s="94"/>
+      <c r="I39" s="85"/>
+      <c r="J39" s="85"/>
+      <c r="K39" s="85"/>
+      <c r="L39" s="85"/>
       <c r="M39" s="88"/>
       <c r="N39" s="88"/>
-      <c r="O39" s="97"/>
+      <c r="O39" s="91"/>
       <c r="P39" s="88"/>
     </row>
     <row r="40" spans="1:16" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -10969,19 +10969,19 @@
       <c r="B40" s="30" t="s">
         <v>599</v>
       </c>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
+      <c r="C40" s="95"/>
+      <c r="D40" s="95"/>
       <c r="E40" s="89"/>
-      <c r="F40" s="86"/>
-      <c r="G40" s="86"/>
-      <c r="H40" s="86"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="86"/>
+      <c r="K40" s="86"/>
+      <c r="L40" s="86"/>
       <c r="M40" s="89"/>
       <c r="N40" s="89"/>
-      <c r="O40" s="98"/>
+      <c r="O40" s="92"/>
       <c r="P40" s="89"/>
     </row>
     <row r="41" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -10992,34 +10992,34 @@
       <c r="B41" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="C41" s="84">
+      <c r="C41" s="93">
         <v>2</v>
       </c>
-      <c r="D41" s="84" t="s">
+      <c r="D41" s="93" t="s">
         <v>628</v>
       </c>
       <c r="E41" s="87" t="s">
         <v>629</v>
       </c>
-      <c r="F41" s="84" t="s">
+      <c r="F41" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G41" s="84"/>
-      <c r="H41" s="84" t="s">
+      <c r="G41" s="93"/>
+      <c r="H41" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I41" s="90">
+      <c r="I41" s="84">
         <v>3</v>
       </c>
-      <c r="J41" s="90">
+      <c r="J41" s="84">
         <f>I41*12</f>
         <v>36</v>
       </c>
-      <c r="K41" s="90">
+      <c r="K41" s="84">
         <f>I41*36</f>
         <v>108</v>
       </c>
-      <c r="L41" s="90">
+      <c r="L41" s="84">
         <f>SUM(J41:K41)</f>
         <v>144</v>
       </c>
@@ -11029,7 +11029,7 @@
       <c r="N41" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O41" s="96" t="s">
+      <c r="O41" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P41" s="87" t="s">
@@ -11044,19 +11044,19 @@
       <c r="B42" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="C42" s="85"/>
-      <c r="D42" s="85"/>
+      <c r="C42" s="94"/>
+      <c r="D42" s="94"/>
       <c r="E42" s="88"/>
-      <c r="F42" s="85"/>
-      <c r="G42" s="85"/>
-      <c r="H42" s="85"/>
-      <c r="I42" s="91"/>
-      <c r="J42" s="91"/>
-      <c r="K42" s="91"/>
-      <c r="L42" s="91"/>
+      <c r="F42" s="94"/>
+      <c r="G42" s="94"/>
+      <c r="H42" s="94"/>
+      <c r="I42" s="85"/>
+      <c r="J42" s="85"/>
+      <c r="K42" s="85"/>
+      <c r="L42" s="85"/>
       <c r="M42" s="88"/>
       <c r="N42" s="88"/>
-      <c r="O42" s="97"/>
+      <c r="O42" s="91"/>
       <c r="P42" s="88"/>
     </row>
     <row r="43" spans="1:16" ht="72" x14ac:dyDescent="0.3">
@@ -11067,19 +11067,19 @@
       <c r="B43" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="C43" s="85"/>
-      <c r="D43" s="85"/>
+      <c r="C43" s="94"/>
+      <c r="D43" s="94"/>
       <c r="E43" s="88"/>
-      <c r="F43" s="85"/>
-      <c r="G43" s="85"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="91"/>
-      <c r="J43" s="91"/>
-      <c r="K43" s="91"/>
-      <c r="L43" s="91"/>
+      <c r="F43" s="94"/>
+      <c r="G43" s="94"/>
+      <c r="H43" s="94"/>
+      <c r="I43" s="85"/>
+      <c r="J43" s="85"/>
+      <c r="K43" s="85"/>
+      <c r="L43" s="85"/>
       <c r="M43" s="88"/>
       <c r="N43" s="88"/>
-      <c r="O43" s="97"/>
+      <c r="O43" s="91"/>
       <c r="P43" s="88"/>
     </row>
     <row r="44" spans="1:16" ht="108" x14ac:dyDescent="0.3">
@@ -11090,19 +11090,19 @@
       <c r="B44" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="C44" s="85"/>
-      <c r="D44" s="85"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
       <c r="E44" s="88"/>
-      <c r="F44" s="85"/>
-      <c r="G44" s="85"/>
-      <c r="H44" s="85"/>
-      <c r="I44" s="91"/>
-      <c r="J44" s="91"/>
-      <c r="K44" s="91"/>
-      <c r="L44" s="91"/>
+      <c r="F44" s="94"/>
+      <c r="G44" s="94"/>
+      <c r="H44" s="94"/>
+      <c r="I44" s="85"/>
+      <c r="J44" s="85"/>
+      <c r="K44" s="85"/>
+      <c r="L44" s="85"/>
       <c r="M44" s="88"/>
       <c r="N44" s="88"/>
-      <c r="O44" s="97"/>
+      <c r="O44" s="91"/>
       <c r="P44" s="88"/>
     </row>
     <row r="45" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -11113,21 +11113,21 @@
       <c r="B45" s="30" t="s">
         <v>598</v>
       </c>
-      <c r="C45" s="86" t="s">
+      <c r="C45" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="86"/>
+      <c r="D45" s="95"/>
       <c r="E45" s="89"/>
-      <c r="F45" s="86"/>
-      <c r="G45" s="86"/>
-      <c r="H45" s="86"/>
-      <c r="I45" s="92"/>
-      <c r="J45" s="92"/>
-      <c r="K45" s="92"/>
-      <c r="L45" s="92"/>
+      <c r="F45" s="95"/>
+      <c r="G45" s="95"/>
+      <c r="H45" s="95"/>
+      <c r="I45" s="86"/>
+      <c r="J45" s="86"/>
+      <c r="K45" s="86"/>
+      <c r="L45" s="86"/>
       <c r="M45" s="89"/>
       <c r="N45" s="89"/>
-      <c r="O45" s="98"/>
+      <c r="O45" s="92"/>
       <c r="P45" s="89"/>
     </row>
     <row r="46" spans="1:16" ht="36" x14ac:dyDescent="0.3">
@@ -11138,34 +11138,34 @@
       <c r="B46" s="31" t="s">
         <v>592</v>
       </c>
-      <c r="C46" s="84">
+      <c r="C46" s="93">
         <v>3</v>
       </c>
-      <c r="D46" s="84" t="s">
+      <c r="D46" s="93" t="s">
         <v>631</v>
       </c>
       <c r="E46" s="87" t="s">
         <v>638</v>
       </c>
-      <c r="F46" s="84" t="s">
+      <c r="F46" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G46" s="84"/>
-      <c r="H46" s="84" t="s">
+      <c r="G46" s="93"/>
+      <c r="H46" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I46" s="84">
+      <c r="I46" s="93">
         <v>3</v>
       </c>
-      <c r="J46" s="84">
+      <c r="J46" s="93">
         <f>12*I46</f>
         <v>36</v>
       </c>
-      <c r="K46" s="84">
+      <c r="K46" s="93">
         <f>36*I46</f>
         <v>108</v>
       </c>
-      <c r="L46" s="84">
+      <c r="L46" s="93">
         <f>SUM(J46:K49)</f>
         <v>144</v>
       </c>
@@ -11175,7 +11175,7 @@
       <c r="N46" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O46" s="96" t="s">
+      <c r="O46" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P46" s="87" t="s">
@@ -11190,19 +11190,19 @@
       <c r="B47" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="C47" s="85"/>
-      <c r="D47" s="85"/>
+      <c r="C47" s="94"/>
+      <c r="D47" s="94"/>
       <c r="E47" s="88"/>
-      <c r="F47" s="85"/>
-      <c r="G47" s="85"/>
-      <c r="H47" s="85"/>
-      <c r="I47" s="85"/>
-      <c r="J47" s="85"/>
-      <c r="K47" s="85"/>
-      <c r="L47" s="85"/>
+      <c r="F47" s="94"/>
+      <c r="G47" s="94"/>
+      <c r="H47" s="94"/>
+      <c r="I47" s="94"/>
+      <c r="J47" s="94"/>
+      <c r="K47" s="94"/>
+      <c r="L47" s="94"/>
       <c r="M47" s="88"/>
       <c r="N47" s="88"/>
-      <c r="O47" s="97"/>
+      <c r="O47" s="91"/>
       <c r="P47" s="88"/>
     </row>
     <row r="48" spans="1:16" ht="72" x14ac:dyDescent="0.3">
@@ -11213,19 +11213,19 @@
       <c r="B48" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="C48" s="85"/>
-      <c r="D48" s="85"/>
+      <c r="C48" s="94"/>
+      <c r="D48" s="94"/>
       <c r="E48" s="88"/>
-      <c r="F48" s="85"/>
-      <c r="G48" s="85"/>
-      <c r="H48" s="85"/>
-      <c r="I48" s="85"/>
-      <c r="J48" s="85"/>
-      <c r="K48" s="85"/>
-      <c r="L48" s="85"/>
+      <c r="F48" s="94"/>
+      <c r="G48" s="94"/>
+      <c r="H48" s="94"/>
+      <c r="I48" s="94"/>
+      <c r="J48" s="94"/>
+      <c r="K48" s="94"/>
+      <c r="L48" s="94"/>
       <c r="M48" s="88"/>
       <c r="N48" s="88"/>
-      <c r="O48" s="97"/>
+      <c r="O48" s="91"/>
       <c r="P48" s="88"/>
     </row>
     <row r="49" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -11236,19 +11236,19 @@
       <c r="B49" s="30" t="s">
         <v>600</v>
       </c>
-      <c r="C49" s="86"/>
-      <c r="D49" s="86"/>
+      <c r="C49" s="95"/>
+      <c r="D49" s="95"/>
       <c r="E49" s="89"/>
-      <c r="F49" s="86"/>
-      <c r="G49" s="86"/>
-      <c r="H49" s="86"/>
-      <c r="I49" s="86"/>
-      <c r="J49" s="86"/>
-      <c r="K49" s="86"/>
-      <c r="L49" s="86"/>
+      <c r="F49" s="95"/>
+      <c r="G49" s="95"/>
+      <c r="H49" s="95"/>
+      <c r="I49" s="95"/>
+      <c r="J49" s="95"/>
+      <c r="K49" s="95"/>
+      <c r="L49" s="95"/>
       <c r="M49" s="89"/>
       <c r="N49" s="89"/>
-      <c r="O49" s="98"/>
+      <c r="O49" s="92"/>
       <c r="P49" s="89"/>
     </row>
     <row r="50" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -11259,34 +11259,34 @@
       <c r="B50" s="31" t="s">
         <v>595</v>
       </c>
-      <c r="C50" s="84">
+      <c r="C50" s="93">
         <v>3</v>
       </c>
-      <c r="D50" s="84" t="s">
+      <c r="D50" s="93" t="s">
         <v>632</v>
       </c>
       <c r="E50" s="87" t="s">
         <v>671</v>
       </c>
-      <c r="F50" s="84" t="s">
+      <c r="F50" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G50" s="84"/>
-      <c r="H50" s="84" t="s">
+      <c r="G50" s="93"/>
+      <c r="H50" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I50" s="90">
+      <c r="I50" s="84">
         <v>3</v>
       </c>
-      <c r="J50" s="90">
+      <c r="J50" s="84">
         <f>I50*12</f>
         <v>36</v>
       </c>
-      <c r="K50" s="90">
+      <c r="K50" s="84">
         <f>I50*36</f>
         <v>108</v>
       </c>
-      <c r="L50" s="90">
+      <c r="L50" s="84">
         <f>SUM(J50:K52)</f>
         <v>144</v>
       </c>
@@ -11296,7 +11296,7 @@
       <c r="N50" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O50" s="96" t="s">
+      <c r="O50" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P50" s="87" t="s">
@@ -11311,19 +11311,19 @@
       <c r="B51" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="C51" s="85"/>
-      <c r="D51" s="85"/>
+      <c r="C51" s="94"/>
+      <c r="D51" s="94"/>
       <c r="E51" s="88"/>
-      <c r="F51" s="85"/>
-      <c r="G51" s="85"/>
-      <c r="H51" s="85"/>
-      <c r="I51" s="91"/>
-      <c r="J51" s="91"/>
-      <c r="K51" s="91"/>
-      <c r="L51" s="91"/>
+      <c r="F51" s="94"/>
+      <c r="G51" s="94"/>
+      <c r="H51" s="94"/>
+      <c r="I51" s="85"/>
+      <c r="J51" s="85"/>
+      <c r="K51" s="85"/>
+      <c r="L51" s="85"/>
       <c r="M51" s="88"/>
       <c r="N51" s="88"/>
-      <c r="O51" s="97"/>
+      <c r="O51" s="91"/>
       <c r="P51" s="88" t="s">
         <v>95</v>
       </c>
@@ -11336,19 +11336,19 @@
       <c r="B52" s="30" t="s">
         <v>598</v>
       </c>
-      <c r="C52" s="86"/>
-      <c r="D52" s="86"/>
+      <c r="C52" s="95"/>
+      <c r="D52" s="95"/>
       <c r="E52" s="89"/>
-      <c r="F52" s="86"/>
-      <c r="G52" s="86"/>
-      <c r="H52" s="86"/>
-      <c r="I52" s="92"/>
-      <c r="J52" s="92"/>
-      <c r="K52" s="92"/>
-      <c r="L52" s="92"/>
+      <c r="F52" s="95"/>
+      <c r="G52" s="95"/>
+      <c r="H52" s="95"/>
+      <c r="I52" s="86"/>
+      <c r="J52" s="86"/>
+      <c r="K52" s="86"/>
+      <c r="L52" s="86"/>
       <c r="M52" s="89"/>
       <c r="N52" s="89"/>
-      <c r="O52" s="98"/>
+      <c r="O52" s="92"/>
       <c r="P52" s="89"/>
     </row>
     <row r="53" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -11359,34 +11359,34 @@
       <c r="B53" s="31" t="s">
         <v>594</v>
       </c>
-      <c r="C53" s="84">
+      <c r="C53" s="93">
         <v>3</v>
       </c>
-      <c r="D53" s="84" t="s">
+      <c r="D53" s="93" t="s">
         <v>633</v>
       </c>
       <c r="E53" s="87" t="s">
         <v>672</v>
       </c>
-      <c r="F53" s="84" t="s">
+      <c r="F53" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G53" s="84"/>
-      <c r="H53" s="84" t="s">
+      <c r="G53" s="93"/>
+      <c r="H53" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I53" s="90">
+      <c r="I53" s="84">
         <v>3</v>
       </c>
-      <c r="J53" s="90">
+      <c r="J53" s="84">
         <f>I53*12</f>
         <v>36</v>
       </c>
-      <c r="K53" s="90">
+      <c r="K53" s="84">
         <f>I53*36</f>
         <v>108</v>
       </c>
-      <c r="L53" s="90">
+      <c r="L53" s="84">
         <f>SUM(J53:K53)</f>
         <v>144</v>
       </c>
@@ -11396,7 +11396,7 @@
       <c r="N53" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O53" s="96" t="s">
+      <c r="O53" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P53" s="87" t="s">
@@ -11411,19 +11411,19 @@
       <c r="B54" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="C54" s="85"/>
-      <c r="D54" s="85"/>
+      <c r="C54" s="94"/>
+      <c r="D54" s="94"/>
       <c r="E54" s="88"/>
-      <c r="F54" s="85"/>
-      <c r="G54" s="85"/>
-      <c r="H54" s="85"/>
-      <c r="I54" s="91"/>
-      <c r="J54" s="91"/>
-      <c r="K54" s="91"/>
-      <c r="L54" s="91"/>
+      <c r="F54" s="94"/>
+      <c r="G54" s="94"/>
+      <c r="H54" s="94"/>
+      <c r="I54" s="85"/>
+      <c r="J54" s="85"/>
+      <c r="K54" s="85"/>
+      <c r="L54" s="85"/>
       <c r="M54" s="88"/>
       <c r="N54" s="88"/>
-      <c r="O54" s="97"/>
+      <c r="O54" s="91"/>
       <c r="P54" s="88"/>
     </row>
     <row r="55" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -11434,19 +11434,19 @@
       <c r="B55" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="C55" s="85"/>
-      <c r="D55" s="85"/>
+      <c r="C55" s="94"/>
+      <c r="D55" s="94"/>
       <c r="E55" s="88"/>
-      <c r="F55" s="85"/>
-      <c r="G55" s="85"/>
-      <c r="H55" s="85"/>
-      <c r="I55" s="91"/>
-      <c r="J55" s="91"/>
-      <c r="K55" s="91"/>
-      <c r="L55" s="91"/>
+      <c r="F55" s="94"/>
+      <c r="G55" s="94"/>
+      <c r="H55" s="94"/>
+      <c r="I55" s="85"/>
+      <c r="J55" s="85"/>
+      <c r="K55" s="85"/>
+      <c r="L55" s="85"/>
       <c r="M55" s="88"/>
       <c r="N55" s="88"/>
-      <c r="O55" s="97"/>
+      <c r="O55" s="91"/>
       <c r="P55" s="88"/>
     </row>
     <row r="56" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -11457,19 +11457,19 @@
       <c r="B56" s="30" t="s">
         <v>600</v>
       </c>
-      <c r="C56" s="86"/>
-      <c r="D56" s="86"/>
+      <c r="C56" s="95"/>
+      <c r="D56" s="95"/>
       <c r="E56" s="89"/>
-      <c r="F56" s="86"/>
-      <c r="G56" s="86"/>
-      <c r="H56" s="86"/>
-      <c r="I56" s="92"/>
-      <c r="J56" s="92"/>
-      <c r="K56" s="92"/>
-      <c r="L56" s="92"/>
+      <c r="F56" s="95"/>
+      <c r="G56" s="95"/>
+      <c r="H56" s="95"/>
+      <c r="I56" s="86"/>
+      <c r="J56" s="86"/>
+      <c r="K56" s="86"/>
+      <c r="L56" s="86"/>
       <c r="M56" s="89"/>
       <c r="N56" s="89"/>
-      <c r="O56" s="98"/>
+      <c r="O56" s="92"/>
       <c r="P56" s="89"/>
     </row>
     <row r="57" spans="1:16" ht="36" x14ac:dyDescent="0.3">
@@ -11480,34 +11480,34 @@
       <c r="B57" s="31" t="s">
         <v>592</v>
       </c>
-      <c r="C57" s="84">
+      <c r="C57" s="93">
         <v>3</v>
       </c>
-      <c r="D57" s="84" t="s">
+      <c r="D57" s="93" t="s">
         <v>634</v>
       </c>
       <c r="E57" s="87" t="s">
         <v>641</v>
       </c>
-      <c r="F57" s="84" t="s">
+      <c r="F57" s="93" t="s">
         <v>615</v>
       </c>
-      <c r="G57" s="84"/>
-      <c r="H57" s="84" t="s">
+      <c r="G57" s="93"/>
+      <c r="H57" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I57" s="90">
+      <c r="I57" s="84">
         <v>2</v>
       </c>
-      <c r="J57" s="90">
+      <c r="J57" s="84">
         <f>I57*12</f>
         <v>24</v>
       </c>
-      <c r="K57" s="90">
+      <c r="K57" s="84">
         <f>I57*36</f>
         <v>72</v>
       </c>
-      <c r="L57" s="90">
+      <c r="L57" s="84">
         <f>SUM(J57:K57)</f>
         <v>96</v>
       </c>
@@ -11517,7 +11517,7 @@
       <c r="N57" s="87" t="s">
         <v>646</v>
       </c>
-      <c r="O57" s="96" t="s">
+      <c r="O57" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P57" s="87" t="s">
@@ -11532,19 +11532,19 @@
       <c r="B58" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="C58" s="85"/>
-      <c r="D58" s="85"/>
+      <c r="C58" s="94"/>
+      <c r="D58" s="94"/>
       <c r="E58" s="88"/>
-      <c r="F58" s="85"/>
-      <c r="G58" s="85"/>
-      <c r="H58" s="85"/>
-      <c r="I58" s="91"/>
-      <c r="J58" s="91"/>
-      <c r="K58" s="91"/>
-      <c r="L58" s="91"/>
+      <c r="F58" s="94"/>
+      <c r="G58" s="94"/>
+      <c r="H58" s="94"/>
+      <c r="I58" s="85"/>
+      <c r="J58" s="85"/>
+      <c r="K58" s="85"/>
+      <c r="L58" s="85"/>
       <c r="M58" s="88"/>
       <c r="N58" s="88"/>
-      <c r="O58" s="97"/>
+      <c r="O58" s="91"/>
       <c r="P58" s="88"/>
     </row>
     <row r="59" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -11555,19 +11555,19 @@
       <c r="B59" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="C59" s="85"/>
-      <c r="D59" s="85"/>
+      <c r="C59" s="94"/>
+      <c r="D59" s="94"/>
       <c r="E59" s="88"/>
-      <c r="F59" s="85"/>
-      <c r="G59" s="85"/>
-      <c r="H59" s="85"/>
-      <c r="I59" s="91"/>
-      <c r="J59" s="91"/>
-      <c r="K59" s="91"/>
-      <c r="L59" s="91"/>
+      <c r="F59" s="94"/>
+      <c r="G59" s="94"/>
+      <c r="H59" s="94"/>
+      <c r="I59" s="85"/>
+      <c r="J59" s="85"/>
+      <c r="K59" s="85"/>
+      <c r="L59" s="85"/>
       <c r="M59" s="88"/>
       <c r="N59" s="88"/>
-      <c r="O59" s="97"/>
+      <c r="O59" s="91"/>
       <c r="P59" s="88"/>
     </row>
     <row r="60" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -11578,19 +11578,19 @@
       <c r="B60" s="30" t="s">
         <v>600</v>
       </c>
-      <c r="C60" s="86"/>
-      <c r="D60" s="86"/>
+      <c r="C60" s="95"/>
+      <c r="D60" s="95"/>
       <c r="E60" s="89"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
-      <c r="H60" s="86"/>
-      <c r="I60" s="92"/>
-      <c r="J60" s="92"/>
-      <c r="K60" s="92"/>
-      <c r="L60" s="92"/>
+      <c r="F60" s="95"/>
+      <c r="G60" s="95"/>
+      <c r="H60" s="95"/>
+      <c r="I60" s="86"/>
+      <c r="J60" s="86"/>
+      <c r="K60" s="86"/>
+      <c r="L60" s="86"/>
       <c r="M60" s="89"/>
       <c r="N60" s="89"/>
-      <c r="O60" s="98"/>
+      <c r="O60" s="92"/>
       <c r="P60" s="89"/>
     </row>
     <row r="61" spans="1:16" ht="54" x14ac:dyDescent="0.3">
@@ -11601,34 +11601,34 @@
       <c r="B61" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="C61" s="84">
+      <c r="C61" s="93">
         <v>3</v>
       </c>
-      <c r="D61" s="84" t="s">
+      <c r="D61" s="93" t="s">
         <v>635</v>
       </c>
       <c r="E61" s="87" t="s">
         <v>636</v>
       </c>
-      <c r="F61" s="84" t="s">
+      <c r="F61" s="93" t="s">
         <v>619</v>
       </c>
-      <c r="G61" s="84"/>
-      <c r="H61" s="84" t="s">
+      <c r="G61" s="93"/>
+      <c r="H61" s="93" t="s">
         <v>616</v>
       </c>
-      <c r="I61" s="90">
+      <c r="I61" s="84">
         <v>3</v>
       </c>
-      <c r="J61" s="90">
+      <c r="J61" s="84">
         <f>I61*12</f>
         <v>36</v>
       </c>
-      <c r="K61" s="90">
+      <c r="K61" s="84">
         <f>I61*36</f>
         <v>108</v>
       </c>
-      <c r="L61" s="90">
+      <c r="L61" s="84">
         <f>SUM(J61:K61)</f>
         <v>144</v>
       </c>
@@ -11638,7 +11638,7 @@
       <c r="N61" s="87" t="s">
         <v>648</v>
       </c>
-      <c r="O61" s="96" t="s">
+      <c r="O61" s="90" t="s">
         <v>617</v>
       </c>
       <c r="P61" s="87" t="s">
@@ -11653,19 +11653,19 @@
       <c r="B62" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="C62" s="85"/>
-      <c r="D62" s="85"/>
+      <c r="C62" s="94"/>
+      <c r="D62" s="94"/>
       <c r="E62" s="88"/>
-      <c r="F62" s="85"/>
-      <c r="G62" s="85"/>
-      <c r="H62" s="85"/>
-      <c r="I62" s="91"/>
-      <c r="J62" s="91"/>
-      <c r="K62" s="91"/>
-      <c r="L62" s="91"/>
+      <c r="F62" s="94"/>
+      <c r="G62" s="94"/>
+      <c r="H62" s="94"/>
+      <c r="I62" s="85"/>
+      <c r="J62" s="85"/>
+      <c r="K62" s="85"/>
+      <c r="L62" s="85"/>
       <c r="M62" s="88"/>
       <c r="N62" s="88"/>
-      <c r="O62" s="97"/>
+      <c r="O62" s="91"/>
       <c r="P62" s="88"/>
     </row>
     <row r="63" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
@@ -11676,21 +11676,21 @@
       <c r="B63" s="30" t="s">
         <v>600</v>
       </c>
-      <c r="C63" s="86" t="s">
+      <c r="C63" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="D63" s="86"/>
+      <c r="D63" s="95"/>
       <c r="E63" s="89"/>
-      <c r="F63" s="86"/>
-      <c r="G63" s="86"/>
-      <c r="H63" s="86"/>
-      <c r="I63" s="92"/>
-      <c r="J63" s="92"/>
-      <c r="K63" s="92"/>
-      <c r="L63" s="92"/>
+      <c r="F63" s="95"/>
+      <c r="G63" s="95"/>
+      <c r="H63" s="95"/>
+      <c r="I63" s="86"/>
+      <c r="J63" s="86"/>
+      <c r="K63" s="86"/>
+      <c r="L63" s="86"/>
       <c r="M63" s="89"/>
       <c r="N63" s="89"/>
-      <c r="O63" s="98"/>
+      <c r="O63" s="92"/>
       <c r="P63" s="89"/>
     </row>
     <row r="64" spans="1:16" ht="36" x14ac:dyDescent="0.3">
@@ -11729,6 +11729,193 @@
     </row>
   </sheetData>
   <mergeCells count="211">
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E24"/>
+    <mergeCell ref="G21:G24"/>
+    <mergeCell ref="H21:H24"/>
+    <mergeCell ref="I21:I24"/>
+    <mergeCell ref="J21:J24"/>
+    <mergeCell ref="K21:K24"/>
+    <mergeCell ref="C34:C37"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="G34:G37"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="I34:I37"/>
+    <mergeCell ref="J34:J37"/>
+    <mergeCell ref="K34:K37"/>
+    <mergeCell ref="C28:C33"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="E28:E33"/>
+    <mergeCell ref="F21:F24"/>
+    <mergeCell ref="F25:F27"/>
+    <mergeCell ref="F28:F33"/>
+    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="I38:I40"/>
+    <mergeCell ref="P38:P40"/>
+    <mergeCell ref="O38:O40"/>
+    <mergeCell ref="N38:N40"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="K25:K27"/>
+    <mergeCell ref="L25:L27"/>
+    <mergeCell ref="M25:M27"/>
+    <mergeCell ref="N25:N27"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="N34:N37"/>
+    <mergeCell ref="O34:O37"/>
+    <mergeCell ref="P34:P37"/>
+    <mergeCell ref="N28:N33"/>
+    <mergeCell ref="G38:G40"/>
+    <mergeCell ref="H38:H40"/>
+    <mergeCell ref="M38:M40"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="M16:M20"/>
+    <mergeCell ref="L16:L20"/>
+    <mergeCell ref="K16:K20"/>
+    <mergeCell ref="J16:J20"/>
+    <mergeCell ref="I16:I20"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="L21:L24"/>
+    <mergeCell ref="M21:M24"/>
+    <mergeCell ref="M34:M37"/>
+    <mergeCell ref="K28:K33"/>
+    <mergeCell ref="L28:L33"/>
+    <mergeCell ref="L34:L37"/>
+    <mergeCell ref="F16:F20"/>
+    <mergeCell ref="F38:F40"/>
+    <mergeCell ref="L38:L40"/>
+    <mergeCell ref="K38:K40"/>
+    <mergeCell ref="J38:J40"/>
+    <mergeCell ref="G28:G33"/>
+    <mergeCell ref="H28:H33"/>
+    <mergeCell ref="I28:I33"/>
+    <mergeCell ref="J28:J33"/>
+    <mergeCell ref="M28:M33"/>
+    <mergeCell ref="C16:C20"/>
+    <mergeCell ref="D16:D20"/>
+    <mergeCell ref="E16:E20"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="N9:N15"/>
+    <mergeCell ref="N16:N20"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="O16:O20"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="C9:C15"/>
+    <mergeCell ref="D9:D15"/>
+    <mergeCell ref="E9:E15"/>
+    <mergeCell ref="G9:G15"/>
+    <mergeCell ref="H9:H15"/>
+    <mergeCell ref="I9:I15"/>
+    <mergeCell ref="J9:J15"/>
+    <mergeCell ref="K9:K15"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="L9:L15"/>
+    <mergeCell ref="M9:M15"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="F9:F15"/>
+    <mergeCell ref="P16:P20"/>
+    <mergeCell ref="O9:O15"/>
+    <mergeCell ref="P9:P15"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="O25:O27"/>
+    <mergeCell ref="P25:P27"/>
+    <mergeCell ref="O21:O24"/>
+    <mergeCell ref="P21:P24"/>
+    <mergeCell ref="N21:N24"/>
+    <mergeCell ref="O28:O33"/>
+    <mergeCell ref="P28:P33"/>
+    <mergeCell ref="L41:L45"/>
+    <mergeCell ref="M41:M45"/>
+    <mergeCell ref="N41:N45"/>
+    <mergeCell ref="O41:O45"/>
+    <mergeCell ref="P41:P45"/>
+    <mergeCell ref="L46:L49"/>
+    <mergeCell ref="M46:M49"/>
+    <mergeCell ref="N46:N49"/>
+    <mergeCell ref="O46:O49"/>
+    <mergeCell ref="P46:P49"/>
+    <mergeCell ref="C41:C45"/>
+    <mergeCell ref="D41:D45"/>
+    <mergeCell ref="E41:E45"/>
+    <mergeCell ref="F41:F45"/>
+    <mergeCell ref="G41:G45"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="G46:G49"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="I46:I49"/>
+    <mergeCell ref="J46:J49"/>
+    <mergeCell ref="K46:K49"/>
+    <mergeCell ref="H41:H45"/>
+    <mergeCell ref="I41:I45"/>
+    <mergeCell ref="J41:J45"/>
+    <mergeCell ref="K41:K45"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="G50:G52"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="I50:I52"/>
+    <mergeCell ref="J50:J52"/>
+    <mergeCell ref="K50:K52"/>
+    <mergeCell ref="M57:M60"/>
+    <mergeCell ref="N57:N60"/>
+    <mergeCell ref="O57:O60"/>
+    <mergeCell ref="P57:P60"/>
+    <mergeCell ref="C53:C56"/>
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="E53:E56"/>
+    <mergeCell ref="F53:F56"/>
+    <mergeCell ref="G53:G56"/>
+    <mergeCell ref="H53:H56"/>
+    <mergeCell ref="I53:I56"/>
+    <mergeCell ref="J53:J56"/>
+    <mergeCell ref="K53:K56"/>
+    <mergeCell ref="L50:L52"/>
+    <mergeCell ref="M50:M52"/>
+    <mergeCell ref="N50:N52"/>
+    <mergeCell ref="O50:O52"/>
+    <mergeCell ref="P50:P52"/>
+    <mergeCell ref="L53:L56"/>
+    <mergeCell ref="M53:M56"/>
+    <mergeCell ref="N53:N56"/>
+    <mergeCell ref="O53:O56"/>
+    <mergeCell ref="P53:P56"/>
     <mergeCell ref="L61:L63"/>
     <mergeCell ref="M61:M63"/>
     <mergeCell ref="N61:N63"/>
@@ -11753,193 +11940,6 @@
     <mergeCell ref="J57:J60"/>
     <mergeCell ref="K57:K60"/>
     <mergeCell ref="L57:L60"/>
-    <mergeCell ref="L50:L52"/>
-    <mergeCell ref="M50:M52"/>
-    <mergeCell ref="N50:N52"/>
-    <mergeCell ref="O50:O52"/>
-    <mergeCell ref="P50:P52"/>
-    <mergeCell ref="L53:L56"/>
-    <mergeCell ref="M53:M56"/>
-    <mergeCell ref="N53:N56"/>
-    <mergeCell ref="O53:O56"/>
-    <mergeCell ref="P53:P56"/>
-    <mergeCell ref="M57:M60"/>
-    <mergeCell ref="N57:N60"/>
-    <mergeCell ref="O57:O60"/>
-    <mergeCell ref="P57:P60"/>
-    <mergeCell ref="C53:C56"/>
-    <mergeCell ref="D53:D56"/>
-    <mergeCell ref="E53:E56"/>
-    <mergeCell ref="F53:F56"/>
-    <mergeCell ref="G53:G56"/>
-    <mergeCell ref="H53:H56"/>
-    <mergeCell ref="I53:I56"/>
-    <mergeCell ref="J53:J56"/>
-    <mergeCell ref="K53:K56"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="G50:G52"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="I50:I52"/>
-    <mergeCell ref="J50:J52"/>
-    <mergeCell ref="K50:K52"/>
-    <mergeCell ref="L46:L49"/>
-    <mergeCell ref="M46:M49"/>
-    <mergeCell ref="N46:N49"/>
-    <mergeCell ref="O46:O49"/>
-    <mergeCell ref="P46:P49"/>
-    <mergeCell ref="C41:C45"/>
-    <mergeCell ref="D41:D45"/>
-    <mergeCell ref="E41:E45"/>
-    <mergeCell ref="F41:F45"/>
-    <mergeCell ref="G41:G45"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="G46:G49"/>
-    <mergeCell ref="H46:H49"/>
-    <mergeCell ref="I46:I49"/>
-    <mergeCell ref="J46:J49"/>
-    <mergeCell ref="K46:K49"/>
-    <mergeCell ref="H41:H45"/>
-    <mergeCell ref="I41:I45"/>
-    <mergeCell ref="J41:J45"/>
-    <mergeCell ref="K41:K45"/>
-    <mergeCell ref="O25:O27"/>
-    <mergeCell ref="P25:P27"/>
-    <mergeCell ref="O21:O24"/>
-    <mergeCell ref="P21:P24"/>
-    <mergeCell ref="N21:N24"/>
-    <mergeCell ref="O28:O33"/>
-    <mergeCell ref="P28:P33"/>
-    <mergeCell ref="L41:L45"/>
-    <mergeCell ref="M41:M45"/>
-    <mergeCell ref="N41:N45"/>
-    <mergeCell ref="O41:O45"/>
-    <mergeCell ref="P41:P45"/>
-    <mergeCell ref="P16:P20"/>
-    <mergeCell ref="O9:O15"/>
-    <mergeCell ref="P9:P15"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="L9:L15"/>
-    <mergeCell ref="M9:M15"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="F9:F15"/>
-    <mergeCell ref="C16:C20"/>
-    <mergeCell ref="D16:D20"/>
-    <mergeCell ref="E16:E20"/>
-    <mergeCell ref="G16:G20"/>
-    <mergeCell ref="N9:N15"/>
-    <mergeCell ref="N16:N20"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="O16:O20"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="C9:C15"/>
-    <mergeCell ref="D9:D15"/>
-    <mergeCell ref="E9:E15"/>
-    <mergeCell ref="G9:G15"/>
-    <mergeCell ref="H9:H15"/>
-    <mergeCell ref="I9:I15"/>
-    <mergeCell ref="J9:J15"/>
-    <mergeCell ref="K9:K15"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="M16:M20"/>
-    <mergeCell ref="L16:L20"/>
-    <mergeCell ref="K16:K20"/>
-    <mergeCell ref="J16:J20"/>
-    <mergeCell ref="I16:I20"/>
-    <mergeCell ref="H16:H20"/>
-    <mergeCell ref="L21:L24"/>
-    <mergeCell ref="M21:M24"/>
-    <mergeCell ref="M34:M37"/>
-    <mergeCell ref="K28:K33"/>
-    <mergeCell ref="L28:L33"/>
-    <mergeCell ref="L34:L37"/>
-    <mergeCell ref="F16:F20"/>
-    <mergeCell ref="F38:F40"/>
-    <mergeCell ref="L38:L40"/>
-    <mergeCell ref="K38:K40"/>
-    <mergeCell ref="J38:J40"/>
-    <mergeCell ref="G28:G33"/>
-    <mergeCell ref="H28:H33"/>
-    <mergeCell ref="I28:I33"/>
-    <mergeCell ref="J28:J33"/>
-    <mergeCell ref="M28:M33"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="I38:I40"/>
-    <mergeCell ref="P38:P40"/>
-    <mergeCell ref="O38:O40"/>
-    <mergeCell ref="N38:N40"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="E25:E27"/>
-    <mergeCell ref="G25:G27"/>
-    <mergeCell ref="H25:H27"/>
-    <mergeCell ref="I25:I27"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="K25:K27"/>
-    <mergeCell ref="L25:L27"/>
-    <mergeCell ref="M25:M27"/>
-    <mergeCell ref="N25:N27"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="N34:N37"/>
-    <mergeCell ref="O34:O37"/>
-    <mergeCell ref="P34:P37"/>
-    <mergeCell ref="N28:N33"/>
-    <mergeCell ref="G38:G40"/>
-    <mergeCell ref="H38:H40"/>
-    <mergeCell ref="M38:M40"/>
-    <mergeCell ref="C21:C24"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E21:E24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="H21:H24"/>
-    <mergeCell ref="I21:I24"/>
-    <mergeCell ref="J21:J24"/>
-    <mergeCell ref="K21:K24"/>
-    <mergeCell ref="C34:C37"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="G34:G37"/>
-    <mergeCell ref="H34:H37"/>
-    <mergeCell ref="I34:I37"/>
-    <mergeCell ref="J34:J37"/>
-    <mergeCell ref="K34:K37"/>
-    <mergeCell ref="C28:C33"/>
-    <mergeCell ref="D28:D33"/>
-    <mergeCell ref="E28:E33"/>
-    <mergeCell ref="F21:F24"/>
-    <mergeCell ref="F25:F27"/>
-    <mergeCell ref="F28:F33"/>
-    <mergeCell ref="F34:F37"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B77" xr:uid="{149936BB-E9F7-467B-9B8A-466861C21273}">
@@ -12205,94 +12205,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.5">
-      <c r="S1" s="128" t="s">
+      <c r="S1" s="125" t="s">
         <v>139</v>
       </c>
-      <c r="T1" s="128"/>
-      <c r="U1" s="128"/>
-      <c r="V1" s="128"/>
-      <c r="W1" s="128"/>
-      <c r="X1" s="128"/>
-      <c r="Y1" s="128"/>
-      <c r="Z1" s="128"/>
-      <c r="AA1" s="128"/>
-      <c r="AB1" s="128"/>
-      <c r="AC1" s="128"/>
-      <c r="AD1" s="128"/>
-      <c r="AE1" s="128"/>
-      <c r="AF1" s="128"/>
-      <c r="AG1" s="128"/>
+      <c r="T1" s="125"/>
+      <c r="U1" s="125"/>
+      <c r="V1" s="125"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
+      <c r="Y1" s="125"/>
+      <c r="Z1" s="125"/>
+      <c r="AA1" s="125"/>
+      <c r="AB1" s="125"/>
+      <c r="AC1" s="125"/>
+      <c r="AD1" s="125"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="125"/>
+      <c r="AG1" s="125"/>
       <c r="AH1" s="9"/>
       <c r="AI1" s="9"/>
       <c r="AJ1" s="9"/>
-      <c r="AL1" s="129" t="s">
+      <c r="AL1" s="130" t="s">
         <v>140</v>
       </c>
-      <c r="AM1" s="129"/>
-      <c r="AN1" s="129"/>
-      <c r="AO1" s="129"/>
-      <c r="AP1" s="129"/>
-      <c r="AQ1" s="129"/>
-      <c r="AR1" s="129"/>
-      <c r="AS1" s="129"/>
-      <c r="AT1" s="129"/>
-      <c r="AU1" s="129"/>
-      <c r="AV1" s="129"/>
-      <c r="AW1" s="129"/>
-      <c r="AX1" s="129"/>
-      <c r="AY1" s="129"/>
-      <c r="AZ1" s="129"/>
+      <c r="AM1" s="130"/>
+      <c r="AN1" s="130"/>
+      <c r="AO1" s="130"/>
+      <c r="AP1" s="130"/>
+      <c r="AQ1" s="130"/>
+      <c r="AR1" s="130"/>
+      <c r="AS1" s="130"/>
+      <c r="AT1" s="130"/>
+      <c r="AU1" s="130"/>
+      <c r="AV1" s="130"/>
+      <c r="AW1" s="130"/>
+      <c r="AX1" s="130"/>
+      <c r="AY1" s="130"/>
+      <c r="AZ1" s="130"/>
       <c r="BA1" s="9"/>
-      <c r="BB1" s="128" t="s">
+      <c r="BB1" s="125" t="s">
         <v>141</v>
       </c>
-      <c r="BC1" s="128"/>
-      <c r="BD1" s="128"/>
-      <c r="BE1" s="128"/>
-      <c r="BF1" s="128"/>
-      <c r="BG1" s="128"/>
+      <c r="BC1" s="125"/>
+      <c r="BD1" s="125"/>
+      <c r="BE1" s="125"/>
+      <c r="BF1" s="125"/>
+      <c r="BG1" s="125"/>
       <c r="BH1" s="9"/>
       <c r="BK1" s="9"/>
     </row>
     <row r="2" spans="1:63" x14ac:dyDescent="0.5">
-      <c r="L2" s="128" t="s">
+      <c r="L2" s="125" t="s">
         <v>142</v>
       </c>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="128"/>
-      <c r="S2" s="130" t="s">
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="125"/>
+      <c r="S2" s="126" t="s">
         <v>143</v>
       </c>
-      <c r="T2" s="130"/>
-      <c r="U2" s="130"/>
-      <c r="V2" s="130"/>
-      <c r="W2" s="130"/>
-      <c r="X2" s="130"/>
-      <c r="Y2" s="130" t="s">
+      <c r="T2" s="126"/>
+      <c r="U2" s="126"/>
+      <c r="V2" s="126"/>
+      <c r="W2" s="126"/>
+      <c r="X2" s="126"/>
+      <c r="Y2" s="126" t="s">
         <v>144</v>
       </c>
-      <c r="Z2" s="130"/>
-      <c r="AA2" s="130"/>
-      <c r="AB2" s="130"/>
-      <c r="AC2" s="130" t="s">
+      <c r="Z2" s="126"/>
+      <c r="AA2" s="126"/>
+      <c r="AB2" s="126"/>
+      <c r="AC2" s="126" t="s">
         <v>145</v>
       </c>
-      <c r="AD2" s="130"/>
-      <c r="AE2" s="130"/>
-      <c r="AF2" s="130"/>
-      <c r="AG2" s="130"/>
+      <c r="AD2" s="126"/>
+      <c r="AE2" s="126"/>
+      <c r="AF2" s="126"/>
+      <c r="AG2" s="126"/>
       <c r="AH2" s="9"/>
       <c r="AI2" s="9"/>
       <c r="AJ2" s="9"/>
-      <c r="AL2" s="129"/>
-      <c r="AM2" s="129"/>
-      <c r="AN2" s="129"/>
-      <c r="AO2" s="129"/>
-      <c r="AP2" s="129"/>
-      <c r="AQ2" s="129"/>
+      <c r="AL2" s="130"/>
+      <c r="AM2" s="130"/>
+      <c r="AN2" s="130"/>
+      <c r="AO2" s="130"/>
+      <c r="AP2" s="130"/>
+      <c r="AQ2" s="130"/>
       <c r="AR2" s="9"/>
       <c r="AS2" s="9"/>
       <c r="AT2" s="9"/>
@@ -12397,29 +12397,29 @@
       <c r="AG3" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AL3" s="125" t="s">
+      <c r="AL3" s="127" t="s">
         <v>174</v>
       </c>
-      <c r="AM3" s="126"/>
-      <c r="AN3" s="126"/>
-      <c r="AO3" s="125" t="s">
+      <c r="AM3" s="128"/>
+      <c r="AN3" s="128"/>
+      <c r="AO3" s="127" t="s">
         <v>175</v>
       </c>
-      <c r="AP3" s="126"/>
-      <c r="AQ3" s="126"/>
-      <c r="AR3" s="125" t="s">
+      <c r="AP3" s="128"/>
+      <c r="AQ3" s="128"/>
+      <c r="AR3" s="127" t="s">
         <v>176</v>
       </c>
-      <c r="AS3" s="126"/>
-      <c r="AT3" s="126"/>
-      <c r="AU3" s="127"/>
-      <c r="AV3" s="125" t="s">
+      <c r="AS3" s="128"/>
+      <c r="AT3" s="128"/>
+      <c r="AU3" s="129"/>
+      <c r="AV3" s="127" t="s">
         <v>177</v>
       </c>
-      <c r="AW3" s="126"/>
-      <c r="AX3" s="126"/>
-      <c r="AY3" s="126"/>
-      <c r="AZ3" s="127"/>
+      <c r="AW3" s="128"/>
+      <c r="AX3" s="128"/>
+      <c r="AY3" s="128"/>
+      <c r="AZ3" s="129"/>
       <c r="BA3" s="10"/>
       <c r="BB3" s="10"/>
       <c r="BC3" s="10"/>
@@ -18468,11 +18468,6 @@
     <sortCondition ref="BC5:BC66"/>
   </sortState>
   <mergeCells count="12">
-    <mergeCell ref="S1:AG1"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="Y2:AB2"/>
-    <mergeCell ref="AC2:AG2"/>
     <mergeCell ref="AV3:AZ3"/>
     <mergeCell ref="AR3:AU3"/>
     <mergeCell ref="AL3:AN3"/>
@@ -18480,6 +18475,11 @@
     <mergeCell ref="BB1:BG1"/>
     <mergeCell ref="AL2:AQ2"/>
     <mergeCell ref="AL1:AZ1"/>
+    <mergeCell ref="S1:AG1"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="AC2:AG2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18545,14 +18545,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="91d06b0e-e43f-423b-9ab9-9a6b45a2a239" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -18751,27 +18749,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="91d06b0e-e43f-423b-9ab9-9a6b45a2a239" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E6A30CB-5911-44D4-B2E2-7F4EC64E8F36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1BD817A-A8ED-4336-8DF7-884CF7731FAE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="91d06b0e-e43f-423b-9ab9-9a6b45a2a239"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -18796,9 +18787,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1BD817A-A8ED-4336-8DF7-884CF7731FAE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E6A30CB-5911-44D4-B2E2-7F4EC64E8F36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5fb26c54-8ae7-4c35-a8dd-e5095fbe886d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="91d06b0e-e43f-423b-9ab9-9a6b45a2a239"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>